--- a/docs/seguimiento/06_Casos_Prueba_y_Defectos_Fase2.xlsx
+++ b/docs/seguimiento/06_Casos_Prueba_y_Defectos_Fase2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan" sheetId="1" r:id="Rffec8c9ba8ef43aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Casos" sheetId="2" r:id="Ree4bb0b60eca4084"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defectos" sheetId="3" r:id="Rb74cbbd2bea04e8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="Rd41c614ad48a4655"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan" sheetId="1" r:id="Reb38cb3018004303"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Casos" sheetId="2" r:id="Re8af69e4b7694817"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defectos" sheetId="3" r:id="Rd1fafc93f22c4429"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" r:id="R21948e621c7d41a3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -370,10 +370,8 @@
       <x:c r="F1" s="16"/>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">El equipo define calidad y aceptación técnica; resultados solo tras ejecutar pruebas.</x:t>
-        </x:is>
+      <x:c r="A2" s="17" t="str">
+        <x:v>Regresión conjunta ejecutada al 20/10/2026. Stripe real y aceptación pendientes.</x:v>
       </x:c>
       <x:c r="B2" s="17"/>
       <x:c r="C2" s="17"/>
@@ -426,7 +424,7 @@
         <x:v>Dobles o datos ficticios</x:v>
       </x:c>
       <x:c r="F5" s="13" t="str">
-        <x:v>EJECUTADO_A / RESTO_PENDIENTE</x:v>
+        <x:v>EJECUTADO_LOCAL / GUIA_04</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
@@ -448,7 +446,7 @@
         </x:is>
       </x:c>
       <x:c r="F6" s="13" t="str">
-        <x:v>EJECUTADO_A / RESTO_PENDIENTE</x:v>
+        <x:v>EJECUTADO_LOCAL / GUIA_04</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="30" customHeight="1">
@@ -470,7 +468,7 @@
         </x:is>
       </x:c>
       <x:c r="F7" s="15" t="str">
-        <x:v>EJECUTADO_A / RESTO_PENDIENTE</x:v>
+        <x:v>EJECUTADO_LOCAL / GUIA_04</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
@@ -490,7 +488,7 @@
         <x:v>Tokens ficticios controlados</x:v>
       </x:c>
       <x:c r="F8" s="13" t="str">
-        <x:v>EJECUTADO_A / RESTO_PENDIENTE</x:v>
+        <x:v>EJECUTADO_LOCAL / GUIA_04</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
@@ -594,7 +592,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="17" t="str">
-        <x:v>Resultados A al 29/09/2026. B/C conservan estado previo; no confundir smoke con aceptación completa.</x:v>
+        <x:v>A/B/C probados al 20/10/2026. E18 note pendiente; E26 solo proveedor simulado.</x:v>
       </x:c>
       <x:c r="B2" s="17"/>
       <x:c r="C2" s="17"/>
@@ -670,7 +668,7 @@
         <x:v>Pública (consola admin)</x:v>
       </x:c>
       <x:c r="G5" s="12" t="str">
-        <x:v>Docker / demo-aprueba-tests / a-sprint1.txt</x:v>
+        <x:v>Docker / demo-aprueba-tests / guía 04</x:v>
       </x:c>
       <x:c r="H5" s="12" t="str">
         <x:v>Status y envelope esperados; respuesta cumple esquema</x:v>
@@ -702,7 +700,7 @@
         <x:v>Bearer admin</x:v>
       </x:c>
       <x:c r="G6" s="14" t="str">
-        <x:v>Solicitud válida según contrato</x:v>
+        <x:v>Docker / demo-aprueba-tests / guía 04</x:v>
       </x:c>
       <x:c r="H6" s="14" t="str">
         <x:v>Status y envelope esperados; respuesta cumple esquema</x:v>
@@ -711,7 +709,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="J6" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>APROBADO_LOCAL</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="30" customHeight="1">
@@ -734,7 +732,7 @@
         <x:v>Bearer finance/admin</x:v>
       </x:c>
       <x:c r="G7" s="12" t="str">
-        <x:v>Solicitud válida según contrato</x:v>
+        <x:v>Docker / demo-aprueba-tests / guía 04</x:v>
       </x:c>
       <x:c r="H7" s="12" t="str">
         <x:v>Status y envelope esperados; respuesta cumple esquema</x:v>
@@ -743,7 +741,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="J7" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>APROBADO_LOCAL</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
@@ -766,7 +764,7 @@
         <x:v>Bearer admin</x:v>
       </x:c>
       <x:c r="G8" s="14" t="str">
-        <x:v>Solicitud válida según contrato</x:v>
+        <x:v>Docker / demo-aprueba-tests / guía 04</x:v>
       </x:c>
       <x:c r="H8" s="14" t="str">
         <x:v>Status y envelope esperados; respuesta cumple esquema</x:v>
@@ -775,7 +773,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="J8" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>APROBADO_LOCAL</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
@@ -798,7 +796,7 @@
         <x:v>Bearer admin</x:v>
       </x:c>
       <x:c r="G9" s="12" t="str">
-        <x:v>Solicitud válida según contrato</x:v>
+        <x:v>Docker / demo-aprueba-tests / guía 04</x:v>
       </x:c>
       <x:c r="H9" s="12" t="str">
         <x:v>Status y envelope esperados; respuesta cumple esquema</x:v>
@@ -807,7 +805,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="J9" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>APROBADO_LOCAL</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
@@ -830,7 +828,7 @@
         <x:v>Bearer admin</x:v>
       </x:c>
       <x:c r="G10" s="14" t="str">
-        <x:v>Solicitud válida según contrato</x:v>
+        <x:v>Docker / demo-aprueba-tests / guía 04</x:v>
       </x:c>
       <x:c r="H10" s="14" t="str">
         <x:v>Status y envelope esperados; respuesta cumple esquema</x:v>
@@ -839,7 +837,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="J10" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>APROBADO_LOCAL</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
@@ -862,7 +860,7 @@
         <x:v>Bearer admin</x:v>
       </x:c>
       <x:c r="G11" s="12" t="str">
-        <x:v>Solicitud válida según contrato</x:v>
+        <x:v>Docker / demo-aprueba-tests / guía 04</x:v>
       </x:c>
       <x:c r="H11" s="12" t="str">
         <x:v>Status y envelope esperados; respuesta cumple esquema</x:v>
@@ -871,7 +869,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="J11" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>APROBADO_LOCAL</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
@@ -894,7 +892,7 @@
         <x:v>Bearer ops/admin</x:v>
       </x:c>
       <x:c r="G12" s="14" t="str">
-        <x:v>Docker / demo-aprueba-tests / a-ops.txt</x:v>
+        <x:v>Docker / demo-aprueba-tests / guía 04</x:v>
       </x:c>
       <x:c r="H12" s="14" t="str">
         <x:v>Status y envelope esperados; respuesta cumple esquema</x:v>
@@ -926,7 +924,7 @@
         <x:v>Bearer ops/admin</x:v>
       </x:c>
       <x:c r="G13" s="12" t="str">
-        <x:v>Docker / demo-aprueba-tests / a-ops.txt</x:v>
+        <x:v>Docker / demo-aprueba-tests / guía 04</x:v>
       </x:c>
       <x:c r="H13" s="12" t="str">
         <x:v>Status y envelope esperados; respuesta cumple esquema</x:v>
@@ -958,7 +956,7 @@
         <x:v>Bearer ops/admin</x:v>
       </x:c>
       <x:c r="G14" s="14" t="str">
-        <x:v>Docker / demo-aprueba-tests / a-ops.txt</x:v>
+        <x:v>Docker / demo-aprueba-tests / guía 04</x:v>
       </x:c>
       <x:c r="H14" s="14" t="str">
         <x:v>Status y envelope esperados; respuesta cumple esquema</x:v>
@@ -990,7 +988,7 @@
         <x:v>Bearer ops/admin</x:v>
       </x:c>
       <x:c r="G15" s="12" t="str">
-        <x:v>Docker / demo-aprueba-tests / a-ops.txt</x:v>
+        <x:v>Docker / demo-aprueba-tests / guía 04</x:v>
       </x:c>
       <x:c r="H15" s="12" t="str">
         <x:v>Status y envelope esperados; respuesta cumple esquema</x:v>
@@ -1022,7 +1020,7 @@
         <x:v>Bearer admin/support</x:v>
       </x:c>
       <x:c r="G16" s="14" t="str">
-        <x:v>Docker / demo-aprueba-tests / a-sprint1.txt</x:v>
+        <x:v>Docker / demo-aprueba-tests / guía 04</x:v>
       </x:c>
       <x:c r="H16" s="14" t="str">
         <x:v>Status y envelope esperados; respuesta cumple esquema</x:v>
@@ -1054,7 +1052,7 @@
         <x:v>Bearer admin/support</x:v>
       </x:c>
       <x:c r="G17" s="12" t="str">
-        <x:v>Docker / demo-aprueba-tests / a-sprint1.txt</x:v>
+        <x:v>Docker / demo-aprueba-tests / guía 04</x:v>
       </x:c>
       <x:c r="H17" s="12" t="str">
         <x:v>Status y envelope esperados; respuesta cumple esquema</x:v>
@@ -1086,7 +1084,7 @@
         <x:v>Bearer admin/support</x:v>
       </x:c>
       <x:c r="G18" s="14" t="str">
-        <x:v>Docker / demo-aprueba-tests / a-sprint2.txt</x:v>
+        <x:v>Docker / demo-aprueba-tests / guía 04</x:v>
       </x:c>
       <x:c r="H18" s="14" t="str">
         <x:v>Status y envelope esperados; respuesta cumple esquema</x:v>
@@ -1118,7 +1116,7 @@
         <x:v>Bearer admin/support</x:v>
       </x:c>
       <x:c r="G19" s="12" t="str">
-        <x:v>Docker / demo-aprueba-tests / a-sprint2.txt</x:v>
+        <x:v>Docker / demo-aprueba-tests / guía 04</x:v>
       </x:c>
       <x:c r="H19" s="12" t="str">
         <x:v>Status y envelope esperados; respuesta cumple esquema</x:v>
@@ -1150,7 +1148,7 @@
         <x:v>Bearer admin/support</x:v>
       </x:c>
       <x:c r="G20" s="14" t="str">
-        <x:v>Docker / demo-aprueba-tests / a-sprint2.txt</x:v>
+        <x:v>Docker / demo-aprueba-tests / guía 04</x:v>
       </x:c>
       <x:c r="H20" s="14" t="str">
         <x:v>Status y envelope esperados; respuesta cumple esquema</x:v>
@@ -1182,7 +1180,7 @@
         <x:v>Bearer admin/support</x:v>
       </x:c>
       <x:c r="G21" s="12" t="str">
-        <x:v>Solicitud válida según contrato</x:v>
+        <x:v>Docker / demo-aprueba-tests / guía 04</x:v>
       </x:c>
       <x:c r="H21" s="12" t="str">
         <x:v>Status y envelope esperados; respuesta cumple esquema</x:v>
@@ -1191,7 +1189,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="J21" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>APROBADO_LOCAL</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="30" customHeight="1">
@@ -1214,7 +1212,7 @@
         <x:v>Bearer admin/support</x:v>
       </x:c>
       <x:c r="G22" s="14" t="str">
-        <x:v>Solicitud válida según contrato</x:v>
+        <x:v>Docker / demo-aprueba-tests / guía 04</x:v>
       </x:c>
       <x:c r="H22" s="14" t="str">
         <x:v>Status y envelope esperados; respuesta cumple esquema</x:v>
@@ -1223,7 +1221,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="J22" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>BASE_APROBADA / NOTE_FALLA</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="30" customHeight="1">
@@ -1246,7 +1244,7 @@
         <x:v>Bearer admin</x:v>
       </x:c>
       <x:c r="G23" s="12" t="str">
-        <x:v>Solicitud válida según contrato</x:v>
+        <x:v>Docker / demo-aprueba-tests / guía 04</x:v>
       </x:c>
       <x:c r="H23" s="12" t="str">
         <x:v>Status y envelope esperados; respuesta cumple esquema</x:v>
@@ -1255,7 +1253,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="J23" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>APROBADO_LOCAL</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="30" customHeight="1">
@@ -1278,7 +1276,7 @@
         <x:v>Bearer admin</x:v>
       </x:c>
       <x:c r="G24" s="14" t="str">
-        <x:v>Solicitud válida según contrato</x:v>
+        <x:v>Docker / demo-aprueba-tests / guía 04</x:v>
       </x:c>
       <x:c r="H24" s="14" t="str">
         <x:v>Status y envelope esperados; respuesta cumple esquema</x:v>
@@ -1287,7 +1285,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="J24" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>APROBADO_LOCAL</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="30" customHeight="1">
@@ -1310,7 +1308,7 @@
         <x:v>Bearer admin</x:v>
       </x:c>
       <x:c r="G25" s="12" t="str">
-        <x:v>Solicitud válida según contrato</x:v>
+        <x:v>Docker / demo-aprueba-tests / guía 04</x:v>
       </x:c>
       <x:c r="H25" s="12" t="str">
         <x:v>Status y envelope esperados; respuesta cumple esquema</x:v>
@@ -1319,7 +1317,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="J25" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>APROBADO_LOCAL</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="30" customHeight="1">
@@ -1342,7 +1340,7 @@
         <x:v>Bearer admin</x:v>
       </x:c>
       <x:c r="G26" s="14" t="str">
-        <x:v>Solicitud válida según contrato</x:v>
+        <x:v>Docker / demo-aprueba-tests / guía 04</x:v>
       </x:c>
       <x:c r="H26" s="14" t="str">
         <x:v>Status y envelope esperados; respuesta cumple esquema</x:v>
@@ -1351,7 +1349,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="J26" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>APROBADO_LOCAL</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="30" customHeight="1">
@@ -1374,7 +1372,7 @@
         <x:v>Bearer admin</x:v>
       </x:c>
       <x:c r="G27" s="12" t="str">
-        <x:v>Solicitud válida según contrato</x:v>
+        <x:v>Docker / demo-aprueba-tests / guía 04</x:v>
       </x:c>
       <x:c r="H27" s="12" t="str">
         <x:v>Status y envelope esperados; respuesta cumple esquema</x:v>
@@ -1383,7 +1381,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="J27" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>APROBADO_LOCAL</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="30" customHeight="1">
@@ -1406,7 +1404,7 @@
         <x:v>Bearer admin</x:v>
       </x:c>
       <x:c r="G28" s="14" t="str">
-        <x:v>Solicitud válida según contrato</x:v>
+        <x:v>Docker / demo-aprueba-tests / guía 04</x:v>
       </x:c>
       <x:c r="H28" s="14" t="str">
         <x:v>Status y envelope esperados; respuesta cumple esquema</x:v>
@@ -1415,7 +1413,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="J28" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>APROBADO_LOCAL</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="30" customHeight="1">
@@ -1438,7 +1436,7 @@
         <x:v>Bearer admin</x:v>
       </x:c>
       <x:c r="G29" s="12" t="str">
-        <x:v>Solicitud válida según contrato</x:v>
+        <x:v>Docker / demo-aprueba-tests / guía 04</x:v>
       </x:c>
       <x:c r="H29" s="12" t="str">
         <x:v>Status y envelope esperados; respuesta cumple esquema</x:v>
@@ -1447,7 +1445,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="J29" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>APROBADO_LOCAL</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="30" customHeight="1">
@@ -1470,7 +1468,7 @@
         <x:v>Bearer admin</x:v>
       </x:c>
       <x:c r="G30" s="14" t="str">
-        <x:v>Solicitud válida según contrato</x:v>
+        <x:v>Docker / demo-aprueba-tests / guía 04</x:v>
       </x:c>
       <x:c r="H30" s="14" t="str">
         <x:v>Status y envelope esperados; respuesta cumple esquema</x:v>
@@ -1479,7 +1477,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="J30" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>APROBADO_SIMULADO</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="30" customHeight="1">
@@ -1502,7 +1500,7 @@
         <x:v>Bearer admin</x:v>
       </x:c>
       <x:c r="G31" s="12" t="str">
-        <x:v>Solicitud válida según contrato</x:v>
+        <x:v>Docker / demo-aprueba-tests / guía 04</x:v>
       </x:c>
       <x:c r="H31" s="12" t="str">
         <x:v>Status y envelope esperados; respuesta cumple esquema</x:v>
@@ -1511,7 +1509,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="J31" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>APROBADO_LOCAL</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="30" customHeight="1">
@@ -1543,7 +1541,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="J32" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>REVISAR_EVIDENCIA / GUIA_04</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="30" customHeight="1">
@@ -1575,7 +1573,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="J33" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>REVISAR_EVIDENCIA / GUIA_04</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="30" customHeight="1">
@@ -1607,7 +1605,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="J34" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>APROBADO_LOCAL</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="30" customHeight="1">
@@ -1639,7 +1637,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="J35" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>APROBADO_LOCAL</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="30" customHeight="1">
@@ -1671,7 +1669,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="J36" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>APROBADO_LOCAL</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="30" customHeight="1">
@@ -1703,7 +1701,7 @@
         <x:v>Integración</x:v>
       </x:c>
       <x:c r="J37" s="15" t="str">
-        <x:v>BLOQUEADO_POR_INSUMO</x:v>
+        <x:v>REVISAR_EVIDENCIA / GUIA_04</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="30" customHeight="1">
@@ -1734,10 +1732,8 @@
       <x:c r="I38" s="14" t="str">
         <x:v>Integración</x:v>
       </x:c>
-      <x:c r="J38" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PLANIFICADO</x:t>
-        </x:is>
+      <x:c r="J38" s="15" t="str">
+        <x:v>APROBADO_LOCAL</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="30" customHeight="1">
@@ -1768,10 +1764,8 @@
       <x:c r="I39" s="12" t="str">
         <x:v>Integración</x:v>
       </x:c>
-      <x:c r="J39" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PLANIFICADO</x:t>
-        </x:is>
+      <x:c r="J39" s="15" t="str">
+        <x:v>APROBADO_LOCAL</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="30" customHeight="1">
@@ -1803,7 +1797,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="J40" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>APROBADO_LOCAL</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="30" customHeight="1">
@@ -1835,7 +1829,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="J41" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>APROBADO_LOCAL</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="30" customHeight="1">
@@ -1866,10 +1860,8 @@
       <x:c r="I42" s="14" t="str">
         <x:v>Integración</x:v>
       </x:c>
-      <x:c r="J42" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PLANIFICADO</x:t>
-        </x:is>
+      <x:c r="J42" s="15" t="str">
+        <x:v>APROBADO_LOCAL</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="30" customHeight="1">
@@ -1901,7 +1893,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="J43" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>REVISAR_EVIDENCIA / GUIA_04</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2007,16 +1999,16 @@
         <x:v>Alta</x:v>
       </x:c>
       <x:c r="F5" s="12" t="str">
-        <x:v>CORREGIDO_LOCAL</x:v>
+        <x:v>CORREGIDO_VERIFICADO_20/10</x:v>
       </x:c>
       <x:c r="G5" s="12" t="str">
         <x:v>Tsung-Hao</x:v>
       </x:c>
       <x:c r="H5" s="12" t="str">
-        <x:v>a-sprint2.txt / contract.txt</x:v>
+        <x:v>../evidencias/integracion/final-contract.txt</x:v>
       </x:c>
       <x:c r="I5" s="12" t="str">
-        <x:v>equipo-a/backend-sprints</x:v>
+        <x:v>db6c916</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
@@ -2036,16 +2028,16 @@
         <x:v>Alta</x:v>
       </x:c>
       <x:c r="F6" s="18" t="str">
-        <x:v>ABIERTO</x:v>
+        <x:v>CORREGIDO_VERIFICADO_20/10</x:v>
       </x:c>
       <x:c r="G6" s="18" t="str">
         <x:v>Felipe</x:v>
       </x:c>
       <x:c r="H6" s="18" t="str">
-        <x:v>contract.txt</x:v>
+        <x:v>../evidencias/integracion/final-contract.txt</x:v>
       </x:c>
       <x:c r="I6" s="18" t="str">
-        <x:v>equipo-a/backend-sprints</x:v>
+        <x:v>db6c916</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="42" customHeight="1">
@@ -2065,16 +2057,16 @@
         <x:v>Alta</x:v>
       </x:c>
       <x:c r="F7" s="18" t="str">
-        <x:v>ABIERTO</x:v>
+        <x:v>CORREGIDO_VERIFICADO_20/10</x:v>
       </x:c>
       <x:c r="G7" s="18" t="str">
         <x:v>Catalina</x:v>
       </x:c>
       <x:c r="H7" s="18" t="str">
-        <x:v>contract.txt</x:v>
+        <x:v>../evidencias/integracion/final-contract.txt</x:v>
       </x:c>
       <x:c r="I7" s="18" t="str">
-        <x:v>equipo-a/backend-sprints</x:v>
+        <x:v>db6c916</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="42" customHeight="1">
@@ -2094,16 +2086,16 @@
         <x:v>Alta</x:v>
       </x:c>
       <x:c r="F8" s="18" t="str">
-        <x:v>ABIERTO</x:v>
+        <x:v>CORREGIDO_VERIFICADO_20/10</x:v>
       </x:c>
       <x:c r="G8" s="18" t="str">
         <x:v>Catalina</x:v>
       </x:c>
       <x:c r="H8" s="18" t="str">
-        <x:v>contract.txt</x:v>
+        <x:v>../evidencias/integracion/final-contract.txt</x:v>
       </x:c>
       <x:c r="I8" s="18" t="str">
-        <x:v>equipo-a/backend-sprints</x:v>
+        <x:v>db6c916</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="42" customHeight="1">
@@ -2123,16 +2115,16 @@
         <x:v>Alta</x:v>
       </x:c>
       <x:c r="F9" s="18" t="str">
-        <x:v>ABIERTO</x:v>
+        <x:v>CORREGIDO_VERIFICADO_20/10</x:v>
       </x:c>
       <x:c r="G9" s="18" t="str">
         <x:v>Catalina</x:v>
       </x:c>
       <x:c r="H9" s="18" t="str">
-        <x:v>contract.txt</x:v>
+        <x:v>../evidencias/integracion/final-contract.txt</x:v>
       </x:c>
       <x:c r="I9" s="18" t="str">
-        <x:v>equipo-a/backend-sprints</x:v>
+        <x:v>db6c916</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="42" customHeight="1">
@@ -2152,16 +2144,16 @@
         <x:v>Alta</x:v>
       </x:c>
       <x:c r="F10" s="18" t="str">
-        <x:v>ABIERTO</x:v>
+        <x:v>CORREGIDO_VERIFICADO_20/10</x:v>
       </x:c>
       <x:c r="G10" s="18" t="str">
         <x:v>Catalina</x:v>
       </x:c>
       <x:c r="H10" s="18" t="str">
-        <x:v>contract.txt</x:v>
+        <x:v>../evidencias/integracion/final-contract.txt</x:v>
       </x:c>
       <x:c r="I10" s="18" t="str">
-        <x:v>equipo-a/backend-sprints</x:v>
+        <x:v>db6c916</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="42" customHeight="1">
@@ -2181,16 +2173,16 @@
         <x:v>Alta</x:v>
       </x:c>
       <x:c r="F11" s="18" t="str">
-        <x:v>ABIERTO</x:v>
+        <x:v>CORREGIDO_VERIFICADO_20/10</x:v>
       </x:c>
       <x:c r="G11" s="18" t="str">
         <x:v>Felipe</x:v>
       </x:c>
       <x:c r="H11" s="18" t="str">
-        <x:v>contract.txt</x:v>
+        <x:v>../evidencias/integracion/final-contract.txt</x:v>
       </x:c>
       <x:c r="I11" s="18" t="str">
-        <x:v>equipo-a/backend-sprints</x:v>
+        <x:v>db6c916</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="42" customHeight="1">
@@ -2210,16 +2202,45 @@
         <x:v>Alta</x:v>
       </x:c>
       <x:c r="F12" s="18" t="str">
-        <x:v>ABIERTO</x:v>
+        <x:v>CORREGIDO_VERIFICADO_20/10</x:v>
       </x:c>
       <x:c r="G12" s="18" t="str">
         <x:v>Felipe</x:v>
       </x:c>
       <x:c r="H12" s="18" t="str">
-        <x:v>contract.txt</x:v>
+        <x:v>../evidencias/integracion/final-contract.txt</x:v>
       </x:c>
       <x:c r="I12" s="18" t="str">
-        <x:v>equipo-a/backend-sprints</x:v>
+        <x:v>db6c916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="18" t="str">
+        <x:v>DEF-E18-NOTE</x:v>
+      </x:c>
+      <x:c r="B13" s="18" t="str">
+        <x:v>2026-10-20</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="str">
+        <x:v>E18</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="str">
+        <x:v>note del contrato se rechaza con 400</x:v>
+      </x:c>
+      <x:c r="E13" s="18" t="str">
+        <x:v>Media</x:v>
+      </x:c>
+      <x:c r="F13" s="18" t="str">
+        <x:v>ABIERTO</x:v>
+      </x:c>
+      <x:c r="G13" s="18" t="str">
+        <x:v>Catalina</x:v>
+      </x:c>
+      <x:c r="H13" s="18" t="str">
+        <x:v>../evidencias/integracion/probe.json</x:v>
+      </x:c>
+      <x:c r="I13" s="18" t="str">
+        <x:v>db6c916</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2324,7 +2345,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="H5" s="13" t="str">
-        <x:v>EJECUTADO_LOCAL / REVISION_PENDIENTE</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
@@ -2350,7 +2371,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="H6" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="30" customHeight="1">
@@ -2376,7 +2397,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="H7" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
@@ -2402,7 +2423,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="H8" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
@@ -2428,7 +2449,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="H9" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
@@ -2454,7 +2475,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="H10" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
@@ -2480,7 +2501,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="H11" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
@@ -2506,7 +2527,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="H12" s="13" t="str">
-        <x:v>EJECUTADO_LOCAL / REVISION_PENDIENTE</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="30" customHeight="1">
@@ -2532,7 +2553,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="H13" s="13" t="str">
-        <x:v>EJECUTADO_LOCAL / REVISION_PENDIENTE</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="30" customHeight="1">
@@ -2558,7 +2579,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="H14" s="13" t="str">
-        <x:v>EJECUTADO_LOCAL / REVISION_PENDIENTE</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="30" customHeight="1">
@@ -2584,7 +2605,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="H15" s="13" t="str">
-        <x:v>EJECUTADO_LOCAL / REVISION_PENDIENTE</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="30" customHeight="1">
@@ -2610,7 +2631,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="H16" s="13" t="str">
-        <x:v>EJECUTADO_LOCAL / REVISION_PENDIENTE</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="30" customHeight="1">
@@ -2636,7 +2657,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="H17" s="13" t="str">
-        <x:v>EJECUTADO_LOCAL / REVISION_PENDIENTE</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="30" customHeight="1">
@@ -2662,7 +2683,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="H18" s="13" t="str">
-        <x:v>EJECUTADO_LOCAL / REVISION_PENDIENTE</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="30" customHeight="1">
@@ -2688,7 +2709,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="H19" s="13" t="str">
-        <x:v>EJECUTADO_LOCAL / REVISION_PENDIENTE</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="30" customHeight="1">
@@ -2714,7 +2735,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="H20" s="13" t="str">
-        <x:v>EJECUTADO_LOCAL / REVISION_PENDIENTE</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="30" customHeight="1">
@@ -2740,7 +2761,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="H21" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="30" customHeight="1">
@@ -2766,7 +2787,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="H22" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PARCIAL / NOTE_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="30" customHeight="1">
@@ -2792,7 +2813,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="H23" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="30" customHeight="1">
@@ -2818,7 +2839,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="H24" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="30" customHeight="1">
@@ -2844,7 +2865,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="H25" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="30" customHeight="1">
@@ -2870,7 +2891,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="H26" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="30" customHeight="1">
@@ -2896,7 +2917,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="H27" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="30" customHeight="1">
@@ -2922,7 +2943,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="H28" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="30" customHeight="1">
@@ -2948,7 +2969,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="H29" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="30" customHeight="1">
@@ -2974,7 +2995,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="H30" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>STRIPE_REAL_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="30" customHeight="1">
@@ -3000,7 +3021,7 @@
         <x:v>Automatizada</x:v>
       </x:c>
       <x:c r="H31" s="13" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
